--- a/healthcare_forms/011_sleep_deprivation_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/011_sleep_deprivation_survey--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_header</t>
+          <t>header_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,40 +561,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>survey_header</t>
+          <t>sleep_duration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sleep Deprivation Survey</t>
+          <t>How do you sleep?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>how_do_you_sleep</t>
+          <t>sleep_length</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How do you sleep?</t>
+          <t>How long do you sleep?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_do_you_sleep</t>
+          <t>tiredness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How do you sleep?</t>
+          <t>Do you have tiredness?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_long_do_you_sleep</t>
+          <t>sleep_quantity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How long do you sleep?</t>
+          <t>How much do you sleep?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness</t>
+          <t>sleep_timing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you have tiredness?</t>
+          <t>Do you usually sleep?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness</t>
+          <t>wake_up_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you have tiredness?</t>
+          <t>What time do you wake up?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,159 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_much_do_you_sleep</t>
+          <t>bedtime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How much do you sleep?</t>
+          <t>What time do you go to bed?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>do_you_sleep</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Do you sleep?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>do_you_sleep</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Do you sleep?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>wake_up_at</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>What time do you wake up?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>wake_up_at</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What time do you wake up?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>bed_time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What time do you go to bed?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>bed_time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What time do you go to bed?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -868,10 +730,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
@@ -896,7 +758,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_duration_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -913,7 +775,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_duration_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -930,7 +792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_duration_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,510 +809,204 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_length_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8_hours_or_less</t>
+          <t>0-4_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8 hours or less</t>
+          <t>0-4 hours</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_length_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9-11_hours</t>
+          <t>4-6_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9-11 hours</t>
+          <t>4-6 hours</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_length_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11-13_hours</t>
+          <t>6-8_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11-13 hours</t>
+          <t>6-8 hours</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>how_do_you_sleep_choices</t>
+          <t>sleep_length_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>more_than_13_hours</t>
+          <t>more_than_8_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>More than 13 hours</t>
+          <t>More than 8 hours</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_long_do_you_sleep_choices</t>
+          <t>tiredness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0-4_hours</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0-4 hours</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_long_do_you_sleep_choices</t>
+          <t>tiredness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4-6_hours</t>
+          <t>difficulty_concentrating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4-6 hours</t>
+          <t>Difficulty concentrating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_long_do_you_sleep_choices</t>
+          <t>tiredness_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6-8_hours</t>
+          <t>memory_problems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6-8 hours</t>
+          <t>Memory problems</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_long_do_you_sleep_choices</t>
+          <t>tiredness_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>more_than_8_hours</t>
+          <t>mood_changes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>More than 8 hours</t>
+          <t>Mood changes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness_choices</t>
+          <t>sleep_timing_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness_choices</t>
+          <t>sleep_timing_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>difficulty_concentrating</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Difficulty concentrating</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness_choices</t>
+          <t>sleep_timing_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>memory_problems</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memory problems</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>do_you_have_tiredness_choices</t>
+          <t>sleep_timing_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mood_changes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mood changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>do_you_have_tiredness_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>do_you_have_tiredness_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sometimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>every_day</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Every day</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2-3_times_a_week</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2-3 times a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1_time_a_week</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1 time a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>do_you_sleep_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>wake_up_at_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6:00_am</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>6:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>wake_up_at_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7:00_am</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>7:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>wake_up_at_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8:00_am</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>wake_up_at_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>9:00_am</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>bed_time_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>11:00_pm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>11:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>bed_time_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10:00_pm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>10:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>bed_time_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>9:00_pm</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>bed_time_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>8:00_pm</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
     </row>
